--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244876</v>
+        <v>122244829</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,29 +805,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575249</v>
+        <v>575269</v>
       </c>
       <c r="R3" t="n">
-        <v>6412343</v>
+        <v>6412377</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122244829</v>
+        <v>122244876</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,33 +919,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575269</v>
+        <v>575249</v>
       </c>
       <c r="R4" t="n">
-        <v>6412377</v>
+        <v>6412343</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,6 +987,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122244957</v>
+        <v>122244829</v>
       </c>
       <c r="B2" t="n">
         <v>57527</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575246</v>
+        <v>575269</v>
       </c>
       <c r="R2" t="n">
-        <v>6412299</v>
+        <v>6412377</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244829</v>
+        <v>122244957</v>
       </c>
       <c r="B3" t="n">
         <v>57527</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575269</v>
+        <v>575246</v>
       </c>
       <c r="R3" t="n">
-        <v>6412377</v>
+        <v>6412299</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122244829</v>
+        <v>122244965</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>57744</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575269</v>
+        <v>575246</v>
       </c>
       <c r="R2" t="n">
-        <v>6412377</v>
+        <v>6412299</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244957</v>
+        <v>122244829</v>
       </c>
       <c r="B3" t="n">
         <v>57527</v>
@@ -824,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -841,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575246</v>
+        <v>575269</v>
       </c>
       <c r="R3" t="n">
-        <v>6412299</v>
+        <v>6412377</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122244876</v>
+        <v>122244957</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,29 +915,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575249</v>
+        <v>575246</v>
       </c>
       <c r="R4" t="n">
-        <v>6412343</v>
+        <v>6412299</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,11 +987,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244965</v>
+        <v>122244876</v>
       </c>
       <c r="B5" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,20 +1025,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,7 +1051,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575246</v>
+        <v>575249</v>
       </c>
       <c r="R5" t="n">
-        <v>6412299</v>
+        <v>6412343</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1102,6 +1097,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122244965</v>
       </c>
       <c r="B2" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>122244829</v>
       </c>
       <c r="B3" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122244957</v>
+        <v>122244876</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,33 +915,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575246</v>
+        <v>575249</v>
       </c>
       <c r="R4" t="n">
-        <v>6412299</v>
+        <v>6412343</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244876</v>
+        <v>122244957</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>57532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,29 +1030,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575249</v>
+        <v>575246</v>
       </c>
       <c r="R5" t="n">
-        <v>6412343</v>
+        <v>6412299</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244829</v>
+        <v>122244957</v>
       </c>
       <c r="B3" t="n">
         <v>57532</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575269</v>
+        <v>575246</v>
       </c>
       <c r="R3" t="n">
-        <v>6412377</v>
+        <v>6412299</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122244876</v>
+        <v>122244829</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,29 +915,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575249</v>
+        <v>575269</v>
       </c>
       <c r="R4" t="n">
-        <v>6412343</v>
+        <v>6412377</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,11 +987,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244957</v>
+        <v>122244876</v>
       </c>
       <c r="B5" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,33 +1029,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575246</v>
+        <v>575249</v>
       </c>
       <c r="R5" t="n">
-        <v>6412299</v>
+        <v>6412343</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1102,6 +1097,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122244965</v>
+        <v>122244957</v>
       </c>
       <c r="B2" t="n">
-        <v>57749</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -785,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244957</v>
+        <v>122244876</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,33 +800,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575246</v>
+        <v>575249</v>
       </c>
       <c r="R3" t="n">
-        <v>6412299</v>
+        <v>6412343</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,11 +912,6 @@
       <c r="E4" t="n">
         <v>103021</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -1013,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244876</v>
+        <v>122244965</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,20 +1015,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,7 +1036,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575249</v>
+        <v>575246</v>
       </c>
       <c r="R5" t="n">
-        <v>6412343</v>
+        <v>6412299</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,11 +1082,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122244957</v>
+        <v>122244965</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -784,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244876</v>
+        <v>122244829</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,24 +801,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575249</v>
+        <v>575269</v>
       </c>
       <c r="R3" t="n">
-        <v>6412343</v>
+        <v>6412377</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,11 +873,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122244829</v>
+        <v>122244876</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,28 +915,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -941,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575269</v>
+        <v>575249</v>
       </c>
       <c r="R4" t="n">
-        <v>6412377</v>
+        <v>6412343</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244965</v>
+        <v>122244957</v>
       </c>
       <c r="B5" t="n">
-        <v>57749</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,28 +1026,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122244965</v>
+        <v>122244829</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575246</v>
+        <v>575269</v>
       </c>
       <c r="R2" t="n">
-        <v>6412299</v>
+        <v>6412377</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244829</v>
+        <v>122244965</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,37 +801,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575269</v>
+        <v>575246</v>
       </c>
       <c r="R3" t="n">
-        <v>6412377</v>
+        <v>6412299</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122244876</v>
+        <v>122244957</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,29 +915,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575249</v>
+        <v>575246</v>
       </c>
       <c r="R4" t="n">
-        <v>6412343</v>
+        <v>6412299</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,11 +987,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244957</v>
+        <v>122244876</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,33 +1029,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575246</v>
+        <v>575249</v>
       </c>
       <c r="R5" t="n">
-        <v>6412299</v>
+        <v>6412343</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1102,6 +1097,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244965</v>
+        <v>122244957</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,33 +801,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122244957</v>
+        <v>122244876</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,33 +919,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575246</v>
+        <v>575249</v>
       </c>
       <c r="R4" t="n">
-        <v>6412299</v>
+        <v>6412343</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,6 +987,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244876</v>
+        <v>122244965</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,20 +1030,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,7 +1056,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575249</v>
+        <v>575246</v>
       </c>
       <c r="R5" t="n">
-        <v>6412343</v>
+        <v>6412299</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122244829</v>
+        <v>122244965</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575269</v>
+        <v>575246</v>
       </c>
       <c r="R2" t="n">
-        <v>6412377</v>
+        <v>6412299</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244957</v>
+        <v>122244829</v>
       </c>
       <c r="B3" t="n">
         <v>57536</v>
@@ -824,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -841,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575246</v>
+        <v>575269</v>
       </c>
       <c r="R3" t="n">
-        <v>6412299</v>
+        <v>6412377</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1018,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244965</v>
+        <v>122244957</v>
       </c>
       <c r="B5" t="n">
-        <v>57753</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,33 +1026,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244829</v>
+        <v>122244876</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,33 +801,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575269</v>
+        <v>575249</v>
       </c>
       <c r="R3" t="n">
-        <v>6412377</v>
+        <v>6412343</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122244876</v>
+        <v>122244957</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,29 +916,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575249</v>
+        <v>575246</v>
       </c>
       <c r="R4" t="n">
-        <v>6412343</v>
+        <v>6412299</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,11 +988,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244957</v>
+        <v>122244829</v>
       </c>
       <c r="B5" t="n">
         <v>57536</v>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575246</v>
+        <v>575269</v>
       </c>
       <c r="R5" t="n">
-        <v>6412299</v>
+        <v>6412377</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 2340-2025 artfynd.xlsx
+++ b/artfynd/A 2340-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122244965</v>
+        <v>122244876</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575246</v>
+        <v>575249</v>
       </c>
       <c r="R2" t="n">
-        <v>6412299</v>
+        <v>6412343</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,32 +785,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122244876</v>
+        <v>122244965</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +818,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575249</v>
+        <v>575246</v>
       </c>
       <c r="R3" t="n">
-        <v>6412343</v>
+        <v>6412299</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,11 +864,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat låga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,15 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122244957</v>
+        <v>122244829</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +920,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -952,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575246</v>
+        <v>575269</v>
       </c>
       <c r="R4" t="n">
-        <v>6412299</v>
+        <v>6412377</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122244829</v>
+        <v>122244957</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,7 +1029,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1066,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575269</v>
+        <v>575246</v>
       </c>
       <c r="R5" t="n">
-        <v>6412377</v>
+        <v>6412299</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1125,6 +1105,350 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94640067</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nagelstad, Hallingeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>575312</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6412158</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 knopp</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94640087</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nagelstad, Hallingeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575325</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6412181</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>94640140</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nagelstad, Hallingeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575336</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6412185</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6 blomknoppar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
